--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2325-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2325-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B021856E-B12D-4645-98A6-9E25B146C5DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F065059-9757-45ED-AB67-7035523D1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{A629D0DF-7405-4B41-B7F1-AEB0070BEDF7}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{76E2979A-021F-493D-8BA4-B808CC0077F1}"/>
   </bookViews>
   <sheets>
     <sheet name="2325-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1562,27 +1562,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D8CB190-2458-484A-BC15-D3C99669DDC7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1936F20C-DDBB-42BA-9680-705E97A10B05}">
   <dimension ref="A1:X43"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1616,7 +1615,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1652,7 +1651,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1704,7 +1703,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1772,7 +1771,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2023</v>
       </c>
@@ -1844,7 +1843,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2022</v>
       </c>
@@ -1916,7 +1915,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2021</v>
       </c>
@@ -1988,7 +1987,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>2020</v>
       </c>
@@ -2060,7 +2059,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2019</v>
       </c>
@@ -2132,7 +2131,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>2018</v>
       </c>
@@ -2204,7 +2203,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2017</v>
       </c>
@@ -2276,7 +2275,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <v>2016</v>
       </c>
@@ -2348,7 +2347,7 @@
         <v>3.72</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2015</v>
       </c>
@@ -2420,7 +2419,7 @@
         <v>8.81</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <v>2014</v>
       </c>
@@ -2492,7 +2491,7 @@
         <v>9.23</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <v>2013</v>
       </c>
@@ -2564,7 +2563,7 @@
         <v>5.08</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>2012</v>
       </c>
@@ -2636,7 +2635,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2011</v>
       </c>
@@ -2708,7 +2707,7 @@
         <v>5.33</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="39">
         <v>2010</v>
       </c>
@@ -2780,7 +2779,7 @@
         <v>7.03</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2009</v>
       </c>
@@ -2852,7 +2851,7 @@
         <v>9.07</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="39">
         <v>2008</v>
       </c>
@@ -2924,7 +2923,7 @@
         <v>7.19</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2007</v>
       </c>
@@ -2996,7 +2995,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="39">
         <v>2006</v>
       </c>
@@ -3068,7 +3067,7 @@
         <v>7.48</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>2005</v>
       </c>
@@ -3140,7 +3139,7 @@
         <v>7.96</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="39">
         <v>2004</v>
       </c>
@@ -3212,7 +3211,7 @@
         <v>7.06</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2003</v>
       </c>
@@ -3284,7 +3283,7 @@
         <v>6.82</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="39">
         <v>2002</v>
       </c>
@@ -3356,7 +3355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <v>2001</v>
       </c>
@@ -3428,7 +3427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="39">
         <v>2000</v>
       </c>
@@ -3500,7 +3499,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>1999</v>
       </c>
@@ -3572,7 +3571,7 @@
         <v>7.87</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="39">
         <v>1998</v>
       </c>
@@ -3644,7 +3643,7 @@
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>1997</v>
       </c>
@@ -3716,7 +3715,7 @@
         <v>8.5500000000000007</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="39">
         <v>1996</v>
       </c>
@@ -3788,7 +3787,7 @@
         <v>7.08</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37">
         <v>1995</v>
       </c>
@@ -3860,7 +3859,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="39">
         <v>1994</v>
       </c>
@@ -3932,7 +3931,7 @@
         <v>6.45</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="37">
         <v>1993</v>
       </c>
@@ -4004,7 +4003,7 @@
         <v>4.41</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="39">
         <v>1992</v>
       </c>
@@ -4076,7 +4075,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="41">
         <v>1991</v>
       </c>
@@ -4148,7 +4147,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="43"/>
       <c r="B38" s="44"/>
       <c r="C38" s="18" t="s">
@@ -4176,7 +4175,7 @@
       <c r="W38" s="50"/>
       <c r="X38" s="46"/>
     </row>
-    <row r="39" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="51">
         <v>1990</v>
       </c>
@@ -4248,7 +4247,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="53"/>
       <c r="B40" s="54"/>
       <c r="C40" s="20" t="s">
@@ -4276,7 +4275,7 @@
       <c r="W40" s="60"/>
       <c r="X40" s="56"/>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="37">
         <v>1989</v>
       </c>
@@ -4348,7 +4347,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="39">
         <v>1987</v>
       </c>
@@ -4420,7 +4419,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="37" t="s">
         <v>56</v>
       </c>
